--- a/小红书笔记数据新增.xlsx
+++ b/小红书笔记数据新增.xlsx
@@ -435,19 +435,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="7"/>
-    <col customWidth="1" max="2" min="2" width="9"/>
+    <col customWidth="1" max="1" min="1" width="6"/>
+    <col customWidth="1" max="2" min="2" width="6"/>
     <col customWidth="1" max="3" min="3" width="15"/>
-    <col customWidth="1" max="4" min="4" width="11"/>
+    <col customWidth="1" max="4" min="4" width="8"/>
     <col customWidth="1" max="5" min="5" width="28"/>
     <col customWidth="1" max="6" min="6" width="44"/>
     <col customWidth="1" max="7" min="7" width="28"/>
     <col customWidth="1" max="8" min="8" width="14"/>
     <col customWidth="1" max="9" min="9" width="7"/>
-    <col customWidth="1" max="10" min="10" width="9"/>
+    <col customWidth="1" max="10" min="10" width="10"/>
     <col customWidth="1" max="11" min="11" width="10"/>
     <col customWidth="1" max="12" min="12" width="7"/>
     <col customWidth="1" max="13" min="13" width="7"/>
@@ -541,485 +541,537 @@
     <row customHeight="1" ht="20" r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Python爬虫真正的高阶玩法🔥</t>
+          <t>很多人说每天发几十条，很容易都是水货。</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>69fe0ce500000000360330d3</t>
+          <t>6a0060e40000000035031342</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0ce500000000360330d3?xsec_token=AB-XGVDyTWQ2dKewBkTJsfeoGUnvCOSq5j6B726lmyMq4=</t>
+          <t>https://www.xiaohongshu.com/explore/6a0060e40000000035031342?xsec_token=ABGxvu9gHOIEmkc40z4UTBjFXyPDMweYkIqz-KKWUh-uQ=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Python自动化实战｜发票PDF批量下载+自动重</t>
+          <t>我的造车故事，藏着 15 年的重量。早期在图纸上推演方向，中期在沉默里等待时机，</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>69fe0b45000000003803582b</t>
+          <t>69fbe939000000002301d71f</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0b45000000003803582b?xsec_token=AB-XGVDyTWQ2dKewBkTJsfeiT0eVYZ45fjgRuNHYc25Gw=</t>
+          <t>https://www.xiaohongshu.com/explore/69fbe939000000002301d71f?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwF27jZka-GbRRfdcRkADUk=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Python自动化｜普通人也能用的8大场景✅</t>
+          <t>我们生活在一个空前伟大的时代，整体的营商环境非常好，但总有人为了自己的利益去刻意</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>69fe0aca00000000360329cf</t>
+          <t>6a041528000000000702e4c4</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0aca00000000360329cf?xsec_token=AB-XGVDyTWQ2dKewBkTJsfektepVTj2ENx8r66s1lUj3k=</t>
+          <t>https://www.xiaohongshu.com/explore/6a041528000000000702e4c4?xsec_token=ABa0pMSawe_djnJN_eW6iQEYJ445_oqJZz7wFUieCGC0c=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Python后端框架选型｜一篇搞定✅</t>
+          <t>真正的领导者是什么？</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69fe0a3a000000003601f547</t>
+          <t>6a0412f100000000070228a2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fe0a3a000000003601f547?xsec_token=AB-XGVDyTWQ2dKewBkTJsfelGYXhDZVjAiBpw7jPlcAIQ=</t>
+          <t>https://www.xiaohongshu.com/explore/6a0412f100000000070228a2?xsec_token=ABa0pMSawe_djnJN_eW6iQEYuaKSaTo4zyCuTpJOH59Ro=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>职场逆袭｜Python搞定所有无脑重复工作</t>
+          <t xml:space="preserve">谁都别来招惹我们！ </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>69fcc51700000000380342ab</t>
+          <t>6a04129100000000080339b7</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fcc51700000000380342ab?xsec_token=AB-w4DjPUYQJStSYryP2oTEhoPqEhPaiwj6i-cHxKcRz4=</t>
+          <t>https://www.xiaohongshu.com/explore/6a04129100000000080339b7?xsec_token=ABa0pMSawe_djnJN_eW6iQEVL0zKy0VUSvHypZWtznrVw=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>职场开挂🔥RPA+AI+Python终结无脑重复工作</t>
+          <t>极少部分媒体的胆子是如何一步步变大的？</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69fcc1a6000000003701e698</t>
+          <t>6a041262000000000803f703</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fcc1a6000000003701e698?xsec_token=AB-w4DjPUYQJStSYryP2oTEin9SpHNblmPMJS5VzTJZQ0=</t>
+          <t>https://www.xiaohongshu.com/explore/6a041262000000000803f703?xsec_token=ABa0pMSawe_djnJN_eW6iQEWXaGBYlIg0Wjokcm95Y31k=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>抖音孵化器运营封神！RPA+爬虫直接把数据效</t>
+          <t>我怎么可能做过医美[黑薯问号R]</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>69fc22b9000000003700d460</t>
+          <t>6a0411cd000000000803f479</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1027,529 +1079,553 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fc22b9000000003700d460?xsec_token=AB-w4DjPUYQJStSYryP2oTEsurYUGKPI-MXQPhOyBbYFg=</t>
+          <t>https://www.xiaohongshu.com/explore/6a0411cd000000000803f479?xsec_token=ABa0pMSawe_djnJN_eW6iQEdoQ1XO61s3qev66QVp1xKw=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>别卷了！RPA+Python+Agent，打工人的AI效率</t>
+          <t>分享出来好像显得我很自恋，但我还是忍不住分享。因为这种传承是我很想看到的！</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69fb6715000000003700fbec</t>
+          <t>6a041147000000000702210a</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fb6715000000003700fbec?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwSZWpuWl4I1VJlylyGjuDQ=</t>
+          <t>https://www.xiaohongshu.com/explore/6a041147000000000702210a?xsec_token=ABa0pMSawe_djnJN_eW6iQEZR1vH-3CLIkcjN3IBNSLKs=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>财务人必看！AI+RPA不是取代你，是帮你把加</t>
+          <t>我听到的是传承的力量！</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69fb61190000000036033051</t>
+          <t>6a0410700000000008033014</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fb61190000000036033051?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwtmSjAnT9cPAPXmG0txono=</t>
+          <t>https://www.xiaohongshu.com/explore/6a0410700000000008033014?xsec_token=ABa0pMSawe_djnJN_eW6iQEU1I3AX4M-R3wDvlhXcX304=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>打工人直接抄！50个RPA核心场景，把重复活</t>
+          <t>听着真的很感动，不是因为帅不帅，而是我最想看到的，一代一代人的传承，这是一种拼搏</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69fb5cf500000000380237d4</t>
+          <t>6a040db6000000000802655c</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fb5cf500000000380237d4?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjzh35rSOJD0u2lfPrvRnkqc=</t>
+          <t>https://www.xiaohongshu.com/explore/6a040db6000000000802655c?xsec_token=ABa0pMSawe_djnJN_eW6iQEdsaF29LivIKHcb59tEG08c=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>电商数据采集天花板：RPA+Python爬虫，规避</t>
+          <t>很多人不喜欢我说话，可是我说的都是大实话。</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69f6a411000000003601f0e5</t>
+          <t>6a03edbf00000000080311ef</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69f6a411000000003601f0e5?xsec_token=ABMbRwbRmouOxCyr3Qw4rO5jJbmKwPCEwe_GxOHe3Fu6A=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03edbf00000000080311ef?xsec_token=ABU1N92RnvLngqUT7UARicyObc1QqHnOn2JnSSl8lARlU=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>干货｜爬虫/数据采集/RPA 优缺点彻底讲明白</t>
+          <t>孩子们看到清华北大和世界各个名校的人，是不是也更有动力考好的大学了呢！</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69f574d000000000380376f7</t>
+          <t>6a03ed7000000000070137a7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69f574d000000000380376f7?xsec_token=ABQpezNZs-QyvSSCcw0Y1eou5yePWNcH51LhhKy6Z677o=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ed7000000000070137a7?xsec_token=ABU1N92RnvLngqUT7UARicyGG4_sQYkmyi0dewM8-NjtQ=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Python自动化 </t>
+          <t>以一己之力提高了短视频平台的学历水平！</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69f573c00000000036033f13</t>
+          <t>6a03ece40000000008024c4b</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69f573c00000000036033f13?xsec_token=ABQpezNZs-QyvSSCcw0Y1eoqQPYPnn7GdIdOODskKVeiU=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ece40000000008024c4b?xsec_token=ABU1N92RnvLngqUT7UARicyP1Fz6lx6AoNpDViEdcWs6E=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>钟帅</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94772868080</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>飞奔的蜗牛</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66954e05000000000303191d</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>影刀RPA和Python有什么区别？</t>
+          <t>金杯银杯不如消费者的口碑！</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69f56c37000000003703536f</t>
+          <t>6a03ec930000000008001a2f</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1557,77 +1633,89 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69f56c37000000003703536f?xsec_token=ABQpezNZs-QyvSSCcw0Y1eojM0gN8T23DGO7q8kyZF5E8=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ec930000000008001a2f?xsec_token=ABU1N92RnvLngqUT7UARicyEWuGbTAUgukMkzRERp8LGg=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>95310701842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>俞浩</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>67ff0050000000001b0328d7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>中国区和全球各个销售大区的销售人员你们头脑风暴出一个老用户最满意的回馈方案！</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6a03ec3f000000000702e8f3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>实话跟你们说，我偷偷在尝试返老还童呢～追觅冰箱 追觅科技 追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6a03e9130000000007028c29</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1635,80 +1723,80 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/6a03e9130000000007028c29?xsec_token=ABU1N92RnvLngqUT7UARicyLgy5TOu0wvWCot1_lNHtY8=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ec3f000000000702e8f3?xsec_token=ABU1N92RnvLngqUT7UARicyKXh9TQ-WdS_dIJeWiOQ1gU=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>无按键一体式机身，从根源上就很难进水藏污，耐用度直接翻倍。追觅科技 追觅牙刷 追</t>
+          <t>第一个务实的用户回馈活动是不是可以有老用户的产品延保，这样一些老产品可以放心无忧</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69ff0ca9000000001f006720</t>
+          <t>6a03ebb0000000000800156d</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1718,148 +1806,148 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69ff0ca9000000001f006720?xsec_token=ABX36zBj4jMIO4gcay5g-dVpMMt6309gyISPo5MLleSMA=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ebb0000000000800156d?xsec_token=ABU1N92RnvLngqUT7UARicyFgI3RyHd-B_lTzTpW8czOo=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>95310701842</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>俞浩</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>67ff0050000000001b0328d7</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>追觅在发展过程中数次遭遇反追觅联盟，别看我嬉皮笑脸，但我已身经百战！</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6a03eafe00000000070247e3</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>给大家安利一款我真的超爱的好物 ——无按键智能电动牙刷！追觅 追觅牙刷 追觅科技</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>69ff0c500000000023005e0a</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69ff0c500000000023005e0a?xsec_token=ABX36zBj4jMIO4gcay5g-dVnFDpdZYSTemSBhVbB1Z7js=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03eafe00000000070247e3?xsec_token=ABU1N92RnvLngqUT7UARicyJ7LmR2ZXaUkMbk4GvdyPTE=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>哇也太高效了吧, 反馈处理速度好快，合适的衣服就安排到位了追觅 追觅科技</t>
+          <t>我想做一些用户回馈活动，像对待员工一样对待用户！</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69ff0c2a000000001f00646d</t>
+          <t>6a03ea750000000008000ee1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1869,2008 +1957,1088 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69ff0c2a000000001f00646d?xsec_token=ABX36zBj4jMIO4gcay5g-dVixMbViuOIUZ-A7V7K4chL0=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ea750000000008000ee1?xsec_token=ABU1N92RnvLngqUT7UARicyFib-SAZ5rpLH3pBjqwKpZ4=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>95310701842</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>俞浩</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>67ff0050000000001b0328d7</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6a03e47b00000000070108ce</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>我的减肥效果必须碾压李飞 追觅 追觅科技常新伟 @李飞</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>69fea00a000000001a02fd3d</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fea00a000000001a02fd3d?xsec_token=AB-XGVDyTWQ2dKewBkTJsfehmZY_Ecb39vsqQmtpxUHT0=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03e47b00000000070108ce?xsec_token=ABU1N92RnvLngqUT7UARicyOkQL1IfAdQJDoc_xkbunqI=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>同事也太贴心了一早把新工服备好放桌上，颜值看着确实超好看～追觅 追觅科技 追觅科</t>
+          <t>网上总有人吐槽我，现实中谁不想要这样的好老板！</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69fe9f9a0000000023017028</t>
+          <t>6a03e048000000000702eb8a</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fe9f9a0000000023017028?xsec_token=AB-XGVDyTWQ2dKewBkTJsfei9vdlNqNGzWrtPFh1-gFwg=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03e048000000000702eb8a?xsec_token=ABU1N92RnvLngqUT7UARicyMcx4UpO1y0TRVM46TklaJc=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>能当上追觅全球总裁，秘诀就两个：战略 + 顶尖核心技术追觅 追觅科技 追觅科技常</t>
+          <t>网上总有人吐槽追觅，现实中谁不想要追觅的产品啊！</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>69fda9080000000022028a0a</t>
+          <t>6a03dff500000000070250dd</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fda9080000000022028a0a?xsec_token=ABWUaXO9siv7J8CIOSOTmh2_z50-DPvfhSBytyfcp4k6U=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03dff500000000070250dd?xsec_token=ABU1N92RnvLngqUT7UARicyI4lg9e0_5J-i6Jjh6zm64c=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>我没俞总那般坎坷低谷，却听过父母当年为 5 块钱买不起药的往事追觅科技常新伟 追</t>
+          <t>很多企业在发展过程中或许曾经都会遇到“专利流氓公司”</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69fda8e00000000023014bd4</t>
+          <t>6a03d542000000000803d956</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fda8e00000000023014bd4?xsec_token=ABWUaXO9siv7J8CIOSOTmh29eSp6YqZrI9pE79Hr_V5gQ=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d542000000000803d956?xsec_token=ABU1N92RnvLngqUT7UARicyAt11xX_tmQW-yDVpn0Lbxc=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>老家北京密云，从小进城叫上北京，妥妥小镇做题家追觅 追觅科技常新伟 北京</t>
+          <t>将百分之三十的资源投入新业务赛道，更能驱动企业持续且创新的高增长</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>69fda8b6000000001f004f71</t>
+          <t>6a03d4920000000007025e13</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fda8b6000000001f004f71?xsec_token=ABWUaXO9siv7J8CIOSOTmh23uCDhmer7S9PC6Qo_XEZTM=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d4920000000007025e13?xsec_token=ABU1N92RnvLngqUT7UARicyD3qdzJxDGZ0JP5IJV50ARs=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>被问怎么考上清华、当上追觅总裁？我其实就是北京密云小镇做题家追觅科技 追觅 追觅</t>
+          <t>我认为将企业30%的资源投入到新业务的创新，这是一个了不起的机制</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>69fda89f0000000022025b1a</t>
+          <t>6a03d37b0000000008025319</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fda89f0000000022025b1a?xsec_token=ABWUaXO9siv7J8CIOSOTmh29iqEYAuB-G9FKACzvc-W14=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d37b0000000008025319?xsec_token=ABU1N92RnvLngqUT7UARicyAkWgq5X9qoaFc56-5YvJjI=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2015年夏天一个闷热的晚上，实验室太无聊了。我打电话给俞老板：俞师兄，我不想努</t>
+          <t>创新，往往需要更大，更自由，很宽松的环境！</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>69fd58d9000000001f0012c0</t>
+          <t>6a03d2f600000000060371ad</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd58d9000000001f0012c0?xsec_token=ABWUaXO9siv7J8CIOSOTmh27BJXWjf73PqdDOBRUuVsqc=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d2f600000000060371ad?xsec_token=ABU1N92RnvLngqUT7UARicyBxDXF8XSCCz3YsPoR-0qNY=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>95310701842</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>俞浩</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>67ff0050000000001b0328d7</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>为了公司我什么都可以牺牲</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>6a03d2bc0000000007025716</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>俞老板是不是知道我特喜欢《海贼王》，当时就被震撼了：改变世界的梦想，原来真能一直</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>69fd58a9000000002300418f</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd58a9000000002300418f?xsec_token=ABWUaXO9siv7J8CIOSOTmh26F_qqwyouN2y-iSKVmRkSo=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d2bc0000000007025716?xsec_token=ABU1N92RnvLngqUT7UARicyOTllpYIxk40LkP1SfGMPR0=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>95310701842</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>俞浩</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>67ff0050000000001b0328d7</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>给大家介绍一款创新的产品，直板夹和吹风机二合一</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6a03d22f000000000702a249</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>好多人问我怎么被“忽悠”进追觅的，许知远也问过。其实特简单：俞老板说，走，去自动</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>69fd58650000000023014179</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd58650000000023014179?xsec_token=ABWUaXO9siv7J8CIOSOTmh28ldfbzPvS8VX_vOpMV53dI=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d22f000000000702a249?xsec_token=ABU1N92RnvLngqUT7UARicyKgNTyA4y9ube0HTszAFx50=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">当时我刚入学，幼小心灵受到一点震撼：清华压力这么大吗？脑子都这么疯狂？追觅科技 </t>
+          <t xml:space="preserve">上市首发全网售罄 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>69fd580b000000001e00ccd1</t>
+          <t>6a03d0990000000008001842</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd580b000000001e00ccd1?xsec_token=ABWUaXO9siv7J8CIOSOTmh24CHeZn6a1zKBmj3kuKKY54=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d0990000000008001842?xsec_token=ABU1N92RnvLngqUT7UARicyKtt1S8_iTlwcLw5jsr9Dqs=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>俞老板在迎新演讲上说，研究生阶段他要冲到校学生会去，带领航院成为清华最强的院系。</t>
+          <t>跟大家分享一个好消息，我们的吹风机cake系列在首发24小时内销售突破2000万</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>69fd57f10000000020038239</t>
+          <t>6a03d0780000000006031026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd57f10000000020038239?xsec_token=ABWUaXO9siv7J8CIOSOTmh2zBIqCuQI4Wcp2ssEu0K7x0=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03d0780000000006031026?xsec_token=ABU1N92RnvLngqUT7UARicyMvVmvIc8AAOr3kO0dZMxx8=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>我08年清华入学，黑话叫“八字班”。俞老板是“五字班”。第一次见他，是他给航院新</t>
+          <t>追觅吹风机 p10 cake</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>69fd577b000000002202b990</t>
+          <t>6a03ce3e000000000603089e</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd577b000000002202b990?xsec_token=ABWUaXO9siv7J8CIOSOTmh25QeOVTsGjj1EDYbgIxkV-c=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03ce3e000000000603089e?xsec_token=ABU1N92RnvLngqUT7UARicyHd0tsW37nB8nmvDOArnBxU=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>42248935879</t>
+          <t>95310701842</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>追觅科技常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>692ef166000000003702bb39</t>
+          <t>67ff0050000000001b0328d7</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>网友问我是不是比俞老板小3岁、是不是真90后？是真的。但凡眼神好使的，都能看出我</t>
+          <t xml:space="preserve">第一时间体验赶海 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>69fd5674000000001a02c5cc</t>
+          <t>6a03cdc200000000070292c5</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>101861</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd5674000000001a02c5cc?xsec_token=ABWUaXO9siv7J8CIOSOTmh24NOYd7MqCjcNIaS2mq0-ls=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03cdc200000000070292c5?xsec_token=ABU1N92RnvLngqUT7UARicyICzDINUGBVuby8xdpSDxn0=</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="20" r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>常新伟</t>
+          <t>俞浩</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>95310701842</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>俞浩</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>67ff0050000000001b0328d7</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>网球局的隐藏视角，被它玩明白了</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>6a03c93600000000070285a9</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>101861</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>134161</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>叫醒我的不是梦想，是整夜在想：前摄上2亿像素行不行？让大家拍出更好看的自己。你们</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>69fd5640000000002301df58</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaohongshu.com/explore/69fd5640000000002301df58?xsec_token=ABWUaXO9siv7J8CIOSOTmh2xQ8kgKvB-JNhdcEaki-sdk=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>想做成事，就把它具象化。比如要超过乔布斯，就把乔布斯放桌上，日思夜想</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>69fd3edc000000001a035bd8</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fd3edc000000001a035bd8?xsec_token=ABWUaXO9siv7J8CIOSOTmh2_KbzdGIrD9MHnEXCz57uig=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>这个也是非常有意义的，而且我喜欢的一个玩偶，这个是乔布斯的玩偶，这个是我们三四年</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>69fc8c530000000036001927</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc8c530000000036001927?xsec_token=AB-w4DjPUYQJStSYryP2oTEsz8U1yjgWyWu6Yv2baqrsk=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>DREAM BOY，我特别喜欢的小玩偶。愿我一直保持好奇、敢于冒险，永远做世界的</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>69fc8a09000000001a035e51</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc8a09000000001a035e51?xsec_token=AB-w4DjPUYQJStSYryP2oTEo-xwJ4VwN-brufegC2pMJc=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>看看追觅全球总裁桌上最新的小摆件，是沃兹先生亲手送给我的。</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>69fc89b4000000001a02d713</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc89b4000000001a02d713?xsec_token=AB-w4DjPUYQJStSYryP2oTErcpOHsPNxsV4b-UaVHyd_U=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>微米级养护精华，滋养头发和头皮。但对我来说，养护过程……地狱难度。追觅科技 追觅</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>69fc77ce000000002202799b</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc77ce000000002202799b?xsec_token=AB-w4DjPUYQJStSYryP2oTEiBKkMCRHoaHcDQ12QFHRU8=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">看看我们雾化的效果。透明，量大、微米级够细，肉眼可见。追觅科技 追觅科技常新伟 </t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>69fc779e000000002301d565</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc779e000000002301d565?xsec_token=AB-w4DjPUYQJStSYryP2oTEqXDIk8vI8jGuelJvXzRclk=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>雾化精华模块，自带追觅精华，还能拆下来换你喜欢的任何精华。追觅科技 追觅科技常新</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>69fc7778000000002202a60b</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc7778000000002202a60b?xsec_token=AB-w4DjPUYQJStSYryP2oTEr0QKb3WHPgdB1EWxF8ze10=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>我们X30的吹风机上独有的雾化技术是微米级的！能让精华更快速更有效的到达目标区域</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>69fc774e000000001a02f4b7</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc774e000000001a02f4b7?xsec_token=AB-w4DjPUYQJStSYryP2oTEnSlDACDTXQrQQS7xfopzJw=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>今天拆箱一个X30吹风机给大家看看。追觅科技 追觅科技常新伟 追觅吹风机 追觅x</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>69fc7730000000001f003891</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc7730000000001f003891?xsec_token=AB-w4DjPUYQJStSYryP2oTElDAIdFjC8u_TfYO0qidgm0=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>扫地机、洗地机的业务月会，真的太无聊了追觅科技常新伟 追觅科技 追觅新品 追觅吹</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>69fc6fad000000003503a489</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc6fad000000003503a489?xsec_token=AB-w4DjPUYQJStSYryP2oTEhMzsATXXZTeKwDweQUPkac=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>开完我们的业务月会了，今天上午的月会是手机汽车大家电的月会，又是干劲满满的一个月</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>69fc1ab4000000003502176f</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fc1ab4000000003502176f?xsec_token=AB-w4DjPUYQJStSYryP2oTErdr6JvMdHLHuiiIAaoLq7A=</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="20" r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>常新伟</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>42248935879</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>追觅科技常新伟</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>692ef166000000003702bb39</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>都在问我头发怎么养护？既然你们诚心诚意地发问，我就严肃认真地回答。如果要保护头发</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>69fbece50000000035039f9f</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>19927</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>43506</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.xiaohongshu.com/explore/69fbece50000000035039f9f?xsec_token=ABHlgWq8Hh-ju_M2dMSmwgjwsZ5NawPdlmNW8E6Y_o_2Y=</t>
+          <t>https://www.xiaohongshu.com/explore/6a03c93600000000070285a9?xsec_token=ABU1N92RnvLngqUT7UARicyJfk5fVpSW46Okwic_TWx9w=</t>
         </is>
       </c>
     </row>
